--- a/01_iskhodnye_dannye.xlsx
+++ b/01_iskhodnye_dannye.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>185000</v>
+        <v>3850000</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42300</v>
+        <v>620000</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25000</v>
+        <v>350000</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>76400</v>
+        <v>1640000</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18650</v>
+        <v>245000</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4200</v>
+        <v>68000</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>60000</v>
+        <v>850000</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>60000</v>
+        <v>850000</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38900</v>
+        <v>540000</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>15300</v>
+        <v>210000</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -770,11 +770,11 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Зарплата за август 2026 (5 сотрудников по 45 000 тенге)</t>
+          <t>Зарплата за август 2026 (5 сотрудников по 350 000 тенге)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>205000</v>
+        <v>1550000</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -795,11 +795,11 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Перечислены страховые взносы с ФОТ за июль 2026</t>
+          <t>Перечислены социальные отчисления и взносы с ФОТ за июль 2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>67500</v>
+        <v>315000</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>8200</v>
+        <v>95000</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>182000</v>
+        <v>2950000</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22000</v>
+        <v>380000</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3100</v>
+        <v>42000</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>51200</v>
+        <v>710000</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4850</v>
+        <v>78000</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9700</v>
+        <v>130000</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -995,11 +995,11 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Уплачен налог по УСН (авансовый платёж за 3 квартал 2026)</t>
+          <t>Уплачен налог по упрощённой декларации СНР (авансовый платёж за 3 квартал 2026)</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>48000</v>
+        <v>620000</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>11200</v>
+        <v>175000</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>96500</v>
+        <v>1680000</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
